--- a/res-exp-ts.xlsx
+++ b/res-exp-ts.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Escritorio\Codi\refprop-python-v2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Codi\refprop-python-v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB8125FA-AB91-4208-B5E6-D0625F0CAAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B737EF0E-710B-47FD-BFB1-A19024D60B5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2D4C2E91-272F-4240-8366-8948133D946D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2D4C2E91-272F-4240-8366-8948133D946D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="154">
   <si>
     <t>Fluido ensayo</t>
   </si>
@@ -456,6 +456,54 @@
   </si>
   <si>
     <t>propane;DME | 0.85;0.15 Qmass</t>
+  </si>
+  <si>
+    <t>EVOLUCIÓN EVAPORADOR</t>
+  </si>
+  <si>
+    <t>Tevap81 (out)</t>
+  </si>
+  <si>
+    <t>Tevap82</t>
+  </si>
+  <si>
+    <t>Tevap83</t>
+  </si>
+  <si>
+    <t>Tevap84</t>
+  </si>
+  <si>
+    <t>Tevap85</t>
+  </si>
+  <si>
+    <t>Tevap86</t>
+  </si>
+  <si>
+    <t>Tevap87</t>
+  </si>
+  <si>
+    <t>Tevap88</t>
+  </si>
+  <si>
+    <t>Tevap89</t>
+  </si>
+  <si>
+    <t>Tevap90</t>
+  </si>
+  <si>
+    <t>Tevap91</t>
+  </si>
+  <si>
+    <t>Tevap92</t>
+  </si>
+  <si>
+    <t>Tevap93</t>
+  </si>
+  <si>
+    <t>Tevap94</t>
+  </si>
+  <si>
+    <t>Tevap95 (in)</t>
   </si>
 </sst>
 </file>
@@ -497,138 +545,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -958,10 +875,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6193BA96-655F-4952-B11B-413C349FA346}">
-  <dimension ref="A1:DH10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:DW10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.28515625" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -992,8 +913,11 @@
       <c r="CR1" t="s">
         <v>8</v>
       </c>
+      <c r="DI1" t="s">
+        <v>138</v>
+      </c>
     </row>
-    <row r="2" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1037,7 +961,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -1374,8 +1298,53 @@
       <c r="DH3" t="s">
         <v>122</v>
       </c>
+      <c r="DI3" t="s">
+        <v>139</v>
+      </c>
+      <c r="DJ3" t="s">
+        <v>140</v>
+      </c>
+      <c r="DK3" t="s">
+        <v>141</v>
+      </c>
+      <c r="DL3" t="s">
+        <v>142</v>
+      </c>
+      <c r="DM3" t="s">
+        <v>143</v>
+      </c>
+      <c r="DN3" t="s">
+        <v>144</v>
+      </c>
+      <c r="DO3" t="s">
+        <v>145</v>
+      </c>
+      <c r="DP3" t="s">
+        <v>146</v>
+      </c>
+      <c r="DQ3" t="s">
+        <v>147</v>
+      </c>
+      <c r="DR3" t="s">
+        <v>148</v>
+      </c>
+      <c r="DS3" t="s">
+        <v>149</v>
+      </c>
+      <c r="DT3" t="s">
+        <v>150</v>
+      </c>
+      <c r="DU3" t="s">
+        <v>151</v>
+      </c>
+      <c r="DV3" t="s">
+        <v>152</v>
+      </c>
+      <c r="DW3" t="s">
+        <v>153</v>
+      </c>
     </row>
-    <row r="4" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>124</v>
       </c>
@@ -1404,10 +1373,10 @@
         <v>386.1775681779211</v>
       </c>
       <c r="J4">
-        <v>2.4003243936035346</v>
+        <v>2.400324393603535</v>
       </c>
       <c r="K4">
-        <v>1.5935265627191098</v>
+        <v>1.5935265627191104</v>
       </c>
       <c r="L4">
         <v>8.2535862080536919</v>
@@ -1416,7 +1385,7 @@
         <v>3.6121989295386498</v>
       </c>
       <c r="N4">
-        <v>0.75864900121062107</v>
+        <v>0.75864900121076673</v>
       </c>
       <c r="O4">
         <v>2.0786972214765314</v>
@@ -1485,7 +1454,7 @@
         <v>25.490254637583892</v>
       </c>
       <c r="AK4">
-        <v>1.5306802900171064</v>
+        <v>1.530680290017107</v>
       </c>
       <c r="AL4">
         <v>365.08169794233925</v>
@@ -1512,7 +1481,7 @@
         <v>2.4246835521712353</v>
       </c>
       <c r="AT4">
-        <v>2.4411895239956762</v>
+        <v>2.4411895239956771</v>
       </c>
       <c r="AU4">
         <v>6.7994322423072102</v>
@@ -1530,7 +1499,7 @@
         <v>0.68310412400041665</v>
       </c>
       <c r="AZ4">
-        <v>2211.7579688596816</v>
+        <v>2211.7579688596825</v>
       </c>
       <c r="BA4">
         <v>0</v>
@@ -1554,19 +1523,19 @@
         <v>572.05630821840646</v>
       </c>
       <c r="BH4">
-        <v>1.5306802900171064</v>
+        <v>1.530680290017107</v>
       </c>
       <c r="BI4">
-        <v>2.4013879672529823</v>
+        <v>2.4013879672529832</v>
       </c>
       <c r="BJ4">
-        <v>3.2332184944982423</v>
+        <v>3.2332184944991518</v>
       </c>
       <c r="BK4">
-        <v>6.9796333602700553</v>
+        <v>6.9796333602709648</v>
       </c>
       <c r="BL4">
-        <v>0.47213141446370183</v>
+        <v>0.47213141446370521</v>
       </c>
       <c r="BM4">
         <v>8.2535862080536919</v>
@@ -1644,22 +1613,22 @@
         <v>4.7255679922820946E-2</v>
       </c>
       <c r="CL4">
-        <v>7.9437394685514597</v>
+        <v>7.9437394685504952</v>
       </c>
       <c r="CM4">
-        <v>17.876845431093436</v>
+        <v>17.876845431093383</v>
       </c>
       <c r="CN4">
-        <v>19.562326019965738</v>
+        <v>19.562326019965298</v>
       </c>
       <c r="CO4">
-        <v>8.8446956201322091E-3</v>
+        <v>8.8446956201320062E-3</v>
       </c>
       <c r="CP4">
         <v>6.6829623446015354E-2</v>
       </c>
       <c r="CQ4">
-        <v>1.2508288501052883E-2</v>
+        <v>1.2508288501052596E-2</v>
       </c>
       <c r="CR4">
         <v>79.850023637583902</v>
@@ -1712,8 +1681,53 @@
       <c r="DH4">
         <v>65.637882067114091</v>
       </c>
+      <c r="DI4">
+        <v>-4.1413386778523495</v>
+      </c>
+      <c r="DJ4">
+        <v>-6.0911409731543626</v>
+      </c>
+      <c r="DK4">
+        <v>-6.6862136845637581</v>
+      </c>
+      <c r="DL4">
+        <v>-7.3649532281879191</v>
+      </c>
+      <c r="DM4">
+        <v>-7.1675652751677852</v>
+      </c>
+      <c r="DN4">
+        <v>-7.4914640939597312</v>
+      </c>
+      <c r="DO4">
+        <v>-7.2990681610738273</v>
+      </c>
+      <c r="DP4">
+        <v>-7.4199388993288586</v>
+      </c>
+      <c r="DQ4">
+        <v>-7.2238579798657705</v>
+      </c>
+      <c r="DR4">
+        <v>-7.2470504765100667</v>
+      </c>
+      <c r="DS4">
+        <v>-7.2454068187919471</v>
+      </c>
+      <c r="DT4">
+        <v>-7.2302698389261755</v>
+      </c>
+      <c r="DU4">
+        <v>-6.8465697852348999</v>
+      </c>
+      <c r="DV4">
+        <v>-6.8620738322147652</v>
+      </c>
+      <c r="DW4">
+        <v>-6.4015990201342285</v>
+      </c>
     </row>
-    <row r="5" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>126</v>
       </c>
@@ -1736,25 +1750,25 @@
         <v>17.860303558823531</v>
       </c>
       <c r="H5">
-        <v>577.49834622146557</v>
+        <v>577.49834622146659</v>
       </c>
       <c r="I5">
-        <v>221.50541218150465</v>
+        <v>221.50541218150576</v>
       </c>
       <c r="J5">
-        <v>1.7862198672252314</v>
+        <v>1.7862198672252365</v>
       </c>
       <c r="K5">
-        <v>0.74781033115655626</v>
+        <v>0.74781033115656104</v>
       </c>
       <c r="L5">
         <v>6.5735326323529417</v>
       </c>
       <c r="M5">
-        <v>3.5160221027397114</v>
+        <v>3.5160221027394272</v>
       </c>
       <c r="N5">
-        <v>0.63154062835624103</v>
+        <v>0.63154062835621971</v>
       </c>
       <c r="O5">
         <v>1.8591322647058774</v>
@@ -1787,7 +1801,7 @@
         <v>307.23999124999995</v>
       </c>
       <c r="Y5">
-        <v>650.03643577743094</v>
+        <v>650.03643577743082</v>
       </c>
       <c r="Z5">
         <v>444.26150966372757</v>
@@ -1799,13 +1813,13 @@
         <v>2.9919189100328217E-2</v>
       </c>
       <c r="AC5">
-        <v>0.31655906467396794</v>
+        <v>0.31655906467396783</v>
       </c>
       <c r="AD5">
-        <v>1.3732643431669307E-2</v>
+        <v>1.3732643431669135E-2</v>
       </c>
       <c r="AE5">
-        <v>2.1157285974809801</v>
+        <v>2.1157285974809796</v>
       </c>
       <c r="AF5">
         <v>1.4459755315584348</v>
@@ -1823,10 +1837,10 @@
         <v>17.860303558823531</v>
       </c>
       <c r="AK5">
-        <v>0.69299356045171989</v>
+        <v>0.69299356045172367</v>
       </c>
       <c r="AL5">
-        <v>203.10345116371127</v>
+        <v>203.10345116371235</v>
       </c>
       <c r="AM5">
         <v>0.68267988235294119</v>
@@ -1841,16 +1855,16 @@
         <v>17.984721897058826</v>
       </c>
       <c r="AQ5">
-        <v>495.92123716860857</v>
+        <v>495.92123716860976</v>
       </c>
       <c r="AR5">
-        <v>604.08792361197595</v>
+        <v>604.08792361197709</v>
       </c>
       <c r="AS5">
-        <v>1.8719651618883382</v>
+        <v>1.8719651618883417</v>
       </c>
       <c r="AT5">
-        <v>1.8585760354194709</v>
+        <v>1.8585760354194758</v>
       </c>
       <c r="AU5">
         <v>8.917400298086898</v>
@@ -1859,19 +1873,19 @@
         <v>6.5735326323529417</v>
       </c>
       <c r="AW5">
-        <v>197.51034529693445</v>
+        <v>197.51034529693436</v>
       </c>
       <c r="AX5">
         <v>307.23999124999995</v>
       </c>
       <c r="AY5">
-        <v>0.64285363534013729</v>
+        <v>0.64285363534013706</v>
       </c>
       <c r="AZ5">
-        <v>1531.7730574720467</v>
+        <v>1531.7730574720463</v>
       </c>
       <c r="BA5">
-        <v>-0.30744092299494025</v>
+        <v>-0.30744092299494075</v>
       </c>
       <c r="BB5">
         <v>-7.4243149558823527</v>
@@ -1886,25 +1900,25 @@
         <v>2.0168122205882351</v>
       </c>
       <c r="BF5">
-        <v>203.10345116371127</v>
+        <v>203.10345116371235</v>
       </c>
       <c r="BG5">
-        <v>488.40490412957809</v>
+        <v>488.40490412957922</v>
       </c>
       <c r="BH5">
-        <v>0.69299356045171989</v>
+        <v>0.69299356045172367</v>
       </c>
       <c r="BI5">
-        <v>1.8442590983716274</v>
+        <v>1.8442590983716309</v>
       </c>
       <c r="BJ5">
-        <v>3.3266235782935052</v>
+        <v>3.3266235782939599</v>
       </c>
       <c r="BK5">
-        <v>8.4003898724111519</v>
+        <v>8.4003898724116066</v>
       </c>
       <c r="BL5">
-        <v>0.36494737701665675</v>
+        <v>0.36494737701666191</v>
       </c>
       <c r="BM5">
         <v>6.5735326323529417</v>
@@ -1925,16 +1939,16 @@
         <v>307.23999124999995</v>
       </c>
       <c r="BS5">
-        <v>520.95511420245373</v>
+        <v>520.95511420245384</v>
       </c>
       <c r="BT5">
         <v>516.62829998938673</v>
       </c>
       <c r="BU5">
-        <v>8.3055412934971359E-3</v>
+        <v>8.3055412934973528E-3</v>
       </c>
       <c r="BV5">
-        <v>1.695596696520391</v>
+        <v>1.6955966965203912</v>
       </c>
       <c r="BW5">
         <v>1.6815138481403236</v>
@@ -1982,22 +1996,22 @@
         <v>4.619423255376353E-2</v>
       </c>
       <c r="CL5">
-        <v>7.9887366683724421</v>
+        <v>7.9887366683729928</v>
       </c>
       <c r="CM5">
-        <v>7.4972631218159549</v>
+        <v>7.4972631218158448</v>
       </c>
       <c r="CN5">
-        <v>10.955768703032204</v>
+        <v>10.955768703032531</v>
       </c>
       <c r="CO5">
-        <v>7.1523445653973025E-3</v>
+        <v>7.1523445653975184E-3</v>
       </c>
       <c r="CP5">
         <v>7.3751055556182207E-2</v>
       </c>
       <c r="CQ5">
-        <v>7.8776783191524865E-3</v>
+        <v>7.8776783191524657E-3</v>
       </c>
       <c r="CR5">
         <v>80.979575249999996</v>
@@ -2050,8 +2064,53 @@
       <c r="DH5">
         <v>65.928752852941173</v>
       </c>
+      <c r="DI5">
+        <v>-4.3910864117647055</v>
+      </c>
+      <c r="DJ5">
+        <v>-6.4351715</v>
+      </c>
+      <c r="DK5">
+        <v>-7.079060882352942</v>
+      </c>
+      <c r="DL5">
+        <v>-7.9475208088235281</v>
+      </c>
+      <c r="DM5">
+        <v>-7.7560015</v>
+      </c>
+      <c r="DN5">
+        <v>-8.224371632352943</v>
+      </c>
+      <c r="DO5">
+        <v>-7.9492112499999985</v>
+      </c>
+      <c r="DP5">
+        <v>-8.1382146617647049</v>
+      </c>
+      <c r="DQ5">
+        <v>-7.9507527941176459</v>
+      </c>
+      <c r="DR5">
+        <v>-7.8155876911764723</v>
+      </c>
+      <c r="DS5">
+        <v>-7.8091490000000006</v>
+      </c>
+      <c r="DT5">
+        <v>-7.8679573382352945</v>
+      </c>
+      <c r="DU5">
+        <v>-7.5284772499999999</v>
+      </c>
+      <c r="DV5">
+        <v>-7.4504925735294121</v>
+      </c>
+      <c r="DW5">
+        <v>-7.4243149558823527</v>
+      </c>
     </row>
-    <row r="6" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>128</v>
       </c>
@@ -2074,25 +2133,25 @@
         <v>18.520104177215192</v>
       </c>
       <c r="H6">
-        <v>579.42257311420678</v>
+        <v>579.42257311420803</v>
       </c>
       <c r="I6">
-        <v>228.44912851082125</v>
+        <v>228.44912851082225</v>
       </c>
       <c r="J6">
-        <v>1.8469144283669079</v>
+        <v>1.8469144283669106</v>
       </c>
       <c r="K6">
-        <v>0.82277801315678634</v>
+        <v>0.82277801315678956</v>
       </c>
       <c r="L6">
         <v>6.3502382911392417</v>
       </c>
       <c r="M6">
-        <v>4.4237733228976168</v>
+        <v>4.4237733228982989</v>
       </c>
       <c r="N6">
-        <v>0.95260029288486336</v>
+        <v>0.95260029288506232</v>
       </c>
       <c r="O6">
         <v>1.989183329113942</v>
@@ -2125,7 +2184,7 @@
         <v>295.8890765063291</v>
       </c>
       <c r="Y6">
-        <v>619.10139085929336</v>
+        <v>619.10139085929382</v>
       </c>
       <c r="Z6">
         <v>441.40330331724323</v>
@@ -2137,13 +2196,13 @@
         <v>2.3260917142936332E-2</v>
       </c>
       <c r="AC6">
-        <v>0.28702582511632019</v>
+        <v>0.28702582511632074</v>
       </c>
       <c r="AD6">
-        <v>-2.8854157217169461E-2</v>
+        <v>-2.8854157217168705E-2</v>
       </c>
       <c r="AE6">
-        <v>2.0923428406660043</v>
+        <v>2.0923428406660061</v>
       </c>
       <c r="AF6">
         <v>1.4917864103976193</v>
@@ -2161,10 +2220,10 @@
         <v>18.520104177215192</v>
       </c>
       <c r="AK6">
-        <v>0.75295700428074164</v>
+        <v>0.75295700428074674</v>
       </c>
       <c r="AL6">
-        <v>205.11868442186105</v>
+        <v>205.11868442186201</v>
       </c>
       <c r="AM6">
         <v>0.95742964556962029</v>
@@ -2179,16 +2238,16 @@
         <v>18.656796379746833</v>
       </c>
       <c r="AQ6">
-        <v>500.83548882556357</v>
+        <v>500.83548882556454</v>
       </c>
       <c r="AR6">
-        <v>606.71657852686803</v>
+        <v>606.71657852686928</v>
       </c>
       <c r="AS6">
-        <v>1.9405619829618916</v>
+        <v>1.9405619829618952</v>
       </c>
       <c r="AT6">
-        <v>1.9214684907237016</v>
+        <v>1.9214684907237067</v>
       </c>
       <c r="AU6">
         <v>8.8305932787821995</v>
@@ -2197,19 +2256,19 @@
         <v>6.3502382911392417</v>
       </c>
       <c r="AW6">
-        <v>186.76948614688121</v>
+        <v>186.76948614688172</v>
       </c>
       <c r="AX6">
         <v>295.8890765063291</v>
       </c>
       <c r="AY6">
-        <v>0.63121453604214472</v>
+        <v>0.6312145360421465</v>
       </c>
       <c r="AZ6">
-        <v>1574.9044388594812</v>
+        <v>1574.9044388594823</v>
       </c>
       <c r="BA6">
-        <v>-0.28793997307424357</v>
+        <v>-0.28793997307424335</v>
       </c>
       <c r="BB6">
         <v>-8.0318850126582273</v>
@@ -2224,25 +2283,25 @@
         <v>2.1127455189873423</v>
       </c>
       <c r="BF6">
-        <v>205.11868442186105</v>
+        <v>205.11868442186201</v>
       </c>
       <c r="BG6">
-        <v>493.32053324150451</v>
+        <v>493.32053324150564</v>
       </c>
       <c r="BH6">
-        <v>0.75295700428074164</v>
+        <v>0.75295700428074674</v>
       </c>
       <c r="BI6">
-        <v>1.9128900458679479</v>
+        <v>1.9128900458679512</v>
       </c>
       <c r="BJ6">
-        <v>3.3842657370829929</v>
+        <v>3.384265737156321</v>
       </c>
       <c r="BK6">
-        <v>8.4381773826526132</v>
+        <v>8.4381773827259412</v>
       </c>
       <c r="BL6">
-        <v>0.35828583949003928</v>
+        <v>0.35828584302660049</v>
       </c>
       <c r="BM6">
         <v>6.3502382911392417</v>
@@ -2263,16 +2322,16 @@
         <v>295.8890765063291</v>
       </c>
       <c r="BS6">
-        <v>508.3751155421175</v>
+        <v>508.37511554211767</v>
       </c>
       <c r="BT6">
         <v>491.24319543857649</v>
       </c>
       <c r="BU6">
-        <v>3.3699368005595608E-2</v>
+        <v>3.3699368005595934E-2</v>
       </c>
       <c r="BV6">
-        <v>1.7181273521303626</v>
+        <v>1.7181273521303631</v>
       </c>
       <c r="BW6">
         <v>1.6602275462104419</v>
@@ -2320,22 +2379,22 @@
         <v>4.6621778017420124E-2</v>
       </c>
       <c r="CL6">
-        <v>7.9210190080745546</v>
+        <v>7.9210190080748086</v>
       </c>
       <c r="CM6">
-        <v>7.8938502271371274</v>
+        <v>7.8938502271375759</v>
       </c>
       <c r="CN6">
-        <v>11.182817781523191</v>
+        <v>11.182817781523688</v>
       </c>
       <c r="CO6">
-        <v>7.1006325879820345E-3</v>
+        <v>7.1006325879823451E-3</v>
       </c>
       <c r="CP6">
         <v>7.6430130052282413E-2</v>
       </c>
       <c r="CQ6">
-        <v>8.0763938753455351E-3</v>
+        <v>8.0763938753455628E-3</v>
       </c>
       <c r="CR6">
         <v>80.083141987341776</v>
@@ -2388,8 +2447,53 @@
       <c r="DH6">
         <v>65.272487075949343</v>
       </c>
+      <c r="DI6">
+        <v>-4.096482</v>
+      </c>
+      <c r="DJ6">
+        <v>-6.473830974683545</v>
+      </c>
+      <c r="DK6">
+        <v>-6.9325119620253171</v>
+      </c>
+      <c r="DL6">
+        <v>-7.8341773544303788</v>
+      </c>
+      <c r="DM6">
+        <v>-7.6847367468354433</v>
+      </c>
+      <c r="DN6">
+        <v>-8.1715939113924065</v>
+      </c>
+      <c r="DO6">
+        <v>-7.9577372151898738</v>
+      </c>
+      <c r="DP6">
+        <v>-8.2034958607594923</v>
+      </c>
+      <c r="DQ6">
+        <v>-8.0803199240506327</v>
+      </c>
+      <c r="DR6">
+        <v>-7.9829687088607582</v>
+      </c>
+      <c r="DS6">
+        <v>-8.0588790632911387</v>
+      </c>
+      <c r="DT6">
+        <v>-8.1667411645569619</v>
+      </c>
+      <c r="DU6">
+        <v>-7.8649979746835417</v>
+      </c>
+      <c r="DV6">
+        <v>-7.8610027848101272</v>
+      </c>
+      <c r="DW6">
+        <v>-8.0318850126582273</v>
+      </c>
     </row>
-    <row r="7" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>130</v>
       </c>
@@ -2412,25 +2516,25 @@
         <v>19.159804560000001</v>
       </c>
       <c r="H7">
-        <v>582.94158791642667</v>
+        <v>582.94158791642769</v>
       </c>
       <c r="I7">
-        <v>235.66970555786315</v>
+        <v>235.66970555786412</v>
       </c>
       <c r="J7">
-        <v>1.8985121497220123</v>
+        <v>1.8985121497220154</v>
       </c>
       <c r="K7">
-        <v>0.88461110003330645</v>
+        <v>0.88461110003330967</v>
       </c>
       <c r="L7">
         <v>6.2194239399999995</v>
       </c>
       <c r="M7">
-        <v>5.0884722576559938</v>
+        <v>5.0884722576520716</v>
       </c>
       <c r="N7">
-        <v>1.1692912281562435</v>
+        <v>1.1692912281562258</v>
       </c>
       <c r="O7">
         <v>2.178377679999997</v>
@@ -2499,10 +2603,10 @@
         <v>19.159804560000001</v>
       </c>
       <c r="AK7">
-        <v>0.79663543477251375</v>
+        <v>0.79663543477251697</v>
       </c>
       <c r="AL7">
-        <v>206.41336934810477</v>
+        <v>206.4133693481057</v>
       </c>
       <c r="AM7">
         <v>0.94102453000000008</v>
@@ -2517,16 +2621,16 @@
         <v>19.271229720000001</v>
       </c>
       <c r="AQ7">
-        <v>505.28944093528202</v>
+        <v>505.28944093528315</v>
       </c>
       <c r="AR7">
-        <v>610.37179348476104</v>
+        <v>610.37179348476207</v>
       </c>
       <c r="AS7">
-        <v>1.9930446704204652</v>
+        <v>1.9930446704204692</v>
       </c>
       <c r="AT7">
-        <v>1.9736064847332928</v>
+        <v>1.9736064847332926</v>
       </c>
       <c r="AU7">
         <v>8.6968581614895832</v>
@@ -2535,19 +2639,19 @@
         <v>6.2194239399999995</v>
       </c>
       <c r="AW7">
-        <v>181.54213864381941</v>
+        <v>181.54213864381919</v>
       </c>
       <c r="AX7">
         <v>287.23538923000001</v>
       </c>
       <c r="AY7">
-        <v>0.63203263055602077</v>
+        <v>0.63203263055601999</v>
       </c>
       <c r="AZ7">
-        <v>1629.4473350583114</v>
+        <v>1629.447335058311</v>
       </c>
       <c r="BA7">
-        <v>-0.26327954595393305</v>
+        <v>-0.26327954595393355</v>
       </c>
       <c r="BB7">
         <v>-8.2779454800000014</v>
@@ -2562,25 +2666,25 @@
         <v>2.2158841000000002</v>
       </c>
       <c r="BF7">
-        <v>206.41336934810477</v>
+        <v>206.4133693481057</v>
       </c>
       <c r="BG7">
-        <v>497.79308079844219</v>
+        <v>497.79308079844321</v>
       </c>
       <c r="BH7">
-        <v>0.79663543477251375</v>
+        <v>0.79663543477251697</v>
       </c>
       <c r="BI7">
-        <v>1.9654411747172635</v>
+        <v>1.9654411747172684</v>
       </c>
       <c r="BJ7">
-        <v>3.1490345247798244</v>
+        <v>3.1490345247503226</v>
       </c>
       <c r="BK7">
-        <v>8.1709710247798242</v>
+        <v>8.1709710247503224</v>
       </c>
       <c r="BL7">
-        <v>0.34851852006831507</v>
+        <v>0.34851852005824713</v>
       </c>
       <c r="BM7">
         <v>6.2194239399999995</v>
@@ -2601,16 +2705,16 @@
         <v>287.23538923000001</v>
       </c>
       <c r="BS7">
-        <v>503.3927647290335</v>
+        <v>503.39276472903356</v>
       </c>
       <c r="BT7">
         <v>487.78143952650339</v>
       </c>
       <c r="BU7">
-        <v>3.1012216099159436E-2</v>
+        <v>3.1012216099159544E-2</v>
       </c>
       <c r="BV7">
-        <v>1.7525443716336369</v>
+        <v>1.7525443716336371</v>
       </c>
       <c r="BW7">
         <v>1.698194086857169</v>
@@ -2658,22 +2762,22 @@
         <v>4.6657408543662855E-2</v>
       </c>
       <c r="CL7">
-        <v>7.9084927185401552</v>
+        <v>7.9084927185405141</v>
       </c>
       <c r="CM7">
-        <v>8.3242593656393407</v>
+        <v>8.3242593656392518</v>
       </c>
       <c r="CN7">
-        <v>11.482053434191855</v>
+        <v>11.482053434192036</v>
       </c>
       <c r="CO7">
-        <v>7.0465937665797332E-3</v>
+        <v>7.0465937665798459E-3</v>
       </c>
       <c r="CP7">
         <v>7.8221047094573767E-2</v>
       </c>
       <c r="CQ7">
-        <v>8.3312342671401432E-3</v>
+        <v>8.3312342671400738E-3</v>
       </c>
       <c r="CR7">
         <v>79.868806790000008</v>
@@ -2726,8 +2830,53 @@
       <c r="DH7">
         <v>64.753085409999997</v>
       </c>
+      <c r="DI7">
+        <v>-4.0809119699999998</v>
+      </c>
+      <c r="DJ7">
+        <v>-6.4943064000000001</v>
+      </c>
+      <c r="DK7">
+        <v>-6.7138458000000014</v>
+      </c>
+      <c r="DL7">
+        <v>-7.6387796699999999</v>
+      </c>
+      <c r="DM7">
+        <v>-7.5072387799999998</v>
+      </c>
+      <c r="DN7">
+        <v>-8.0463170399999999</v>
+      </c>
+      <c r="DO7">
+        <v>-7.8531028499999991</v>
+      </c>
+      <c r="DP7">
+        <v>-8.1547690100000008</v>
+      </c>
+      <c r="DQ7">
+        <v>-8.0962641200000007</v>
+      </c>
+      <c r="DR7">
+        <v>-8.0197509099999991</v>
+      </c>
+      <c r="DS7">
+        <v>-8.1271447600000002</v>
+      </c>
+      <c r="DT7">
+        <v>-8.3093498799999992</v>
+      </c>
+      <c r="DU7">
+        <v>-8.0848040700000006</v>
+      </c>
+      <c r="DV7">
+        <v>-8.1019463800000011</v>
+      </c>
+      <c r="DW7">
+        <v>-8.2779454800000014</v>
+      </c>
     </row>
-    <row r="8" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>132</v>
       </c>
@@ -2750,25 +2899,25 @@
         <v>20.063725557142856</v>
       </c>
       <c r="H8">
-        <v>588.48446257392322</v>
+        <v>588.48446257392413</v>
       </c>
       <c r="I8">
-        <v>243.64187532697071</v>
+        <v>243.64187532697159</v>
       </c>
       <c r="J8">
-        <v>1.9484568257608468</v>
+        <v>1.9484568257608499</v>
       </c>
       <c r="K8">
-        <v>0.94306576160550448</v>
+        <v>0.94306576160550781</v>
       </c>
       <c r="L8">
         <v>6.2937181571428571</v>
       </c>
       <c r="M8">
-        <v>6.0169728907998206</v>
+        <v>6.0169728907980584</v>
       </c>
       <c r="N8">
-        <v>1.5647269009871927</v>
+        <v>1.5647269009871252</v>
       </c>
       <c r="O8">
         <v>2.2461628142857251</v>
@@ -2801,7 +2950,7 @@
         <v>293.40716052857141</v>
       </c>
       <c r="Y8">
-        <v>602.87279242007355</v>
+        <v>602.87279242007367</v>
       </c>
       <c r="Z8">
         <v>447.50344738182207</v>
@@ -2813,13 +2962,13 @@
         <v>3.7456631488171126E-2</v>
       </c>
       <c r="AC8">
-        <v>0.25771497236516894</v>
+        <v>0.25771497236516905</v>
       </c>
       <c r="AD8">
-        <v>-7.1207182637901517E-2</v>
+        <v>-7.1207182637901323E-2</v>
       </c>
       <c r="AE8">
-        <v>2.0547310138375678</v>
+        <v>2.0547310138375683</v>
       </c>
       <c r="AF8">
         <v>1.5251960673885636</v>
@@ -2837,10 +2986,10 @@
         <v>20.063725557142856</v>
       </c>
       <c r="AK8">
-        <v>0.85503712989600822</v>
+        <v>0.85503712989601166</v>
       </c>
       <c r="AL8">
-        <v>214.38305452452298</v>
+        <v>214.38305452452332</v>
       </c>
       <c r="AM8">
         <v>1.4056243714285714</v>
@@ -2855,16 +3004,16 @@
         <v>20.165733385714287</v>
       </c>
       <c r="AQ8">
-        <v>510.42147174578139</v>
+        <v>510.42147174578224</v>
       </c>
       <c r="AR8">
-        <v>616.32092077134826</v>
+        <v>616.32092077134928</v>
       </c>
       <c r="AS8">
-        <v>2.0418577460886893</v>
+        <v>2.0418577460886915</v>
       </c>
       <c r="AT8">
-        <v>2.0244198021013986</v>
+        <v>2.0244198021014017</v>
       </c>
       <c r="AU8">
         <v>8.656265534091018</v>
@@ -2873,19 +3022,19 @@
         <v>6.2937181571428571</v>
       </c>
       <c r="AW8">
-        <v>185.13924587878739</v>
+        <v>185.13924587878768</v>
       </c>
       <c r="AX8">
         <v>293.40716052857141</v>
       </c>
       <c r="AY8">
-        <v>0.63099770825381374</v>
+        <v>0.63099770825381474</v>
       </c>
       <c r="AZ8">
-        <v>1692.7989974959498</v>
+        <v>1692.7989974959507</v>
       </c>
       <c r="BA8">
-        <v>-0.23463641983905317</v>
+        <v>-0.23463641983905306</v>
       </c>
       <c r="BB8">
         <v>-8.8125735000000009</v>
@@ -2900,25 +3049,25 @@
         <v>2.3296112285714283</v>
       </c>
       <c r="BF8">
-        <v>214.38305452452298</v>
+        <v>214.38305452452332</v>
       </c>
       <c r="BG8">
-        <v>503.18496718345796</v>
+        <v>503.18496718345892</v>
       </c>
       <c r="BH8">
-        <v>0.85503712989600822</v>
+        <v>0.85503712989601166</v>
       </c>
       <c r="BI8">
-        <v>2.0152662081054813</v>
+        <v>2.0152662081054848</v>
       </c>
       <c r="BJ8">
-        <v>3.5114281641084819</v>
+        <v>3.51142816409393</v>
       </c>
       <c r="BK8">
-        <v>8.3382549498227672</v>
+        <v>8.3382549498082152</v>
       </c>
       <c r="BL8">
-        <v>0.35400106145617477</v>
+        <v>0.35400106145044657</v>
       </c>
       <c r="BM8">
         <v>6.2937181571428571</v>
@@ -2939,16 +3088,16 @@
         <v>293.40716052857141</v>
       </c>
       <c r="BS8">
-        <v>504.89940042197901</v>
+        <v>504.89940042198015</v>
       </c>
       <c r="BT8">
         <v>506.05246736598906</v>
       </c>
       <c r="BU8">
-        <v>-2.2837558195679228E-3</v>
+        <v>-2.2837558195656664E-3</v>
       </c>
       <c r="BV8">
-        <v>1.7208148550717217</v>
+        <v>1.7208148550717257</v>
       </c>
       <c r="BW8">
         <v>1.7247447760113908</v>
@@ -2996,22 +3145,22 @@
         <v>4.5915274447466556E-2</v>
       </c>
       <c r="CL8">
-        <v>7.9150231983303625</v>
+        <v>7.9150231983298003</v>
       </c>
       <c r="CM8">
-        <v>8.7920647347753036</v>
+        <v>8.792064734775316</v>
       </c>
       <c r="CN8">
-        <v>11.829961729886843</v>
+        <v>11.829961729886477</v>
       </c>
       <c r="CO8">
-        <v>6.988403081160938E-3</v>
+        <v>6.9884030811607186E-3</v>
       </c>
       <c r="CP8">
         <v>7.7564080384557171E-2</v>
       </c>
       <c r="CQ8">
-        <v>8.627464611234946E-3</v>
+        <v>8.6274646112347222E-3</v>
       </c>
       <c r="CR8">
         <v>81.010793357142859</v>
@@ -3064,8 +3213,53 @@
       <c r="DH8">
         <v>64.542306985714276</v>
       </c>
+      <c r="DI8">
+        <v>-3.4212024142857143</v>
+      </c>
+      <c r="DJ8">
+        <v>-5.8000311857142854</v>
+      </c>
+      <c r="DK8">
+        <v>-6.7340165142857158</v>
+      </c>
+      <c r="DL8">
+        <v>-7.7097396285714286</v>
+      </c>
+      <c r="DM8">
+        <v>-7.6035061714285703</v>
+      </c>
+      <c r="DN8">
+        <v>-7.8928564000000003</v>
+      </c>
+      <c r="DO8">
+        <v>-8.005132699999999</v>
+      </c>
+      <c r="DP8">
+        <v>-8.3795460571428553</v>
+      </c>
+      <c r="DQ8">
+        <v>-8.3693920142857152</v>
+      </c>
+      <c r="DR8">
+        <v>-8.3450393857142871</v>
+      </c>
+      <c r="DS8">
+        <v>-8.5097773571428572</v>
+      </c>
+      <c r="DT8">
+        <v>-8.7194117428571474</v>
+      </c>
+      <c r="DU8">
+        <v>-8.6748374285714291</v>
+      </c>
+      <c r="DV8">
+        <v>-8.5391127142857144</v>
+      </c>
+      <c r="DW8">
+        <v>-8.8125735000000009</v>
+      </c>
     </row>
-    <row r="9" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>134</v>
       </c>
@@ -3088,25 +3282,25 @@
         <v>20.231399573033709</v>
       </c>
       <c r="H9">
-        <v>593.60945630666981</v>
+        <v>593.60945630667061</v>
       </c>
       <c r="I9">
-        <v>253.89061651574539</v>
+        <v>253.89061651574605</v>
       </c>
       <c r="J9">
-        <v>1.9984563740217853</v>
+        <v>1.9984563740217895</v>
       </c>
       <c r="K9">
-        <v>1.0049600741984488</v>
+        <v>1.0049600741984523</v>
       </c>
       <c r="L9">
         <v>6.4355025280898879</v>
       </c>
       <c r="M9">
-        <v>4.3715327868552549</v>
+        <v>4.3715327868565055</v>
       </c>
       <c r="N9">
-        <v>1.0278383348512676</v>
+        <v>1.0278383348517437</v>
       </c>
       <c r="O9">
         <v>1.9461283764044879</v>
@@ -3139,7 +3333,7 @@
         <v>297.31723310112363</v>
       </c>
       <c r="Y9">
-        <v>607.29484786507157</v>
+        <v>607.29484786507192</v>
       </c>
       <c r="Z9">
         <v>445.21292672384908</v>
@@ -3151,13 +3345,13 @@
         <v>3.2133825449351942E-2</v>
       </c>
       <c r="AC9">
-        <v>0.26689164532025433</v>
+        <v>0.26689164532025472</v>
       </c>
       <c r="AD9">
-        <v>-5.7951172096971482E-2</v>
+        <v>-5.7951172096970885E-2</v>
       </c>
       <c r="AE9">
-        <v>2.0425820647218194</v>
+        <v>2.0425820647218207</v>
       </c>
       <c r="AF9">
         <v>1.4974339767665708</v>
@@ -3169,16 +3363,16 @@
         <v>0.15575784190716307</v>
       </c>
       <c r="AI9">
-        <v>56.089971460674164</v>
+        <v>58</v>
       </c>
       <c r="AJ9">
         <v>20.231399573033709</v>
       </c>
       <c r="AK9">
-        <v>0.92931805570296211</v>
+        <v>0.92</v>
       </c>
       <c r="AL9">
-        <v>228.64268881232425</v>
+        <v>228.64268881232513</v>
       </c>
       <c r="AM9">
         <v>0.61233551685393262</v>
@@ -3193,16 +3387,16 @@
         <v>20.411021168539325</v>
       </c>
       <c r="AQ9">
-        <v>513.85027043503533</v>
+        <v>513.85027043503612</v>
       </c>
       <c r="AR9">
-        <v>620.34226212837609</v>
+        <v>620.34226212837677</v>
       </c>
       <c r="AS9">
-        <v>2.0836949561790266</v>
+        <v>2.0836949561790297</v>
       </c>
       <c r="AT9">
-        <v>2.0709668948594793</v>
+        <v>2.0709668948594819</v>
       </c>
       <c r="AU9">
         <v>8.4882454856331417</v>
@@ -3211,19 +3405,19 @@
         <v>6.4355025280898879</v>
       </c>
       <c r="AW9">
-        <v>190.36930048995052</v>
+        <v>190.36930048995032</v>
       </c>
       <c r="AX9">
         <v>297.31723310112363</v>
       </c>
       <c r="AY9">
-        <v>0.64029016584182341</v>
+        <v>0.64029016584182274</v>
       </c>
       <c r="AZ9">
-        <v>1720.8537973626983</v>
+        <v>1720.8537973626999</v>
       </c>
       <c r="BA9">
-        <v>-0.22195203019889165</v>
+        <v>-0.22195203019889123</v>
       </c>
       <c r="BB9">
         <v>-8.356580584269663</v>
@@ -3238,25 +3432,25 @@
         <v>2.4046219213483147</v>
       </c>
       <c r="BF9">
-        <v>228.64268881232425</v>
+        <v>228.64268881232513</v>
       </c>
       <c r="BG9">
-        <v>506.30793994478984</v>
+        <v>506.30793994479063</v>
       </c>
       <c r="BH9">
-        <v>0.92931805570296211</v>
+        <v>0.92931805570296433</v>
       </c>
       <c r="BI9">
-        <v>2.0558886369755425</v>
+        <v>2.0558886369755451</v>
       </c>
       <c r="BJ9">
-        <v>2.7472197361726822</v>
+        <v>2.7472197361835393</v>
       </c>
       <c r="BK9">
-        <v>7.7671971519030203</v>
+        <v>7.7671971519138774</v>
       </c>
       <c r="BL9">
-        <v>0.37609922873155316</v>
+        <v>0.3760992287344968</v>
       </c>
       <c r="BM9">
         <v>6.4355025280898879</v>
@@ -3277,16 +3471,16 @@
         <v>297.31723310112363</v>
       </c>
       <c r="BS9">
-        <v>496.36539600713775</v>
+        <v>496.36539600713763</v>
       </c>
       <c r="BT9">
         <v>507.3876361042341</v>
       </c>
       <c r="BU9">
-        <v>-2.2205899496140255E-2</v>
+        <v>-2.2205899496140487E-2</v>
       </c>
       <c r="BV9">
-        <v>1.669480745632776</v>
+        <v>1.6694807456327756</v>
       </c>
       <c r="BW9">
         <v>1.7065530672810387</v>
@@ -3334,22 +3528,22 @@
         <v>4.6112687641662077E-2</v>
       </c>
       <c r="CL9">
-        <v>7.8762621682899798</v>
+        <v>7.8762621682895153</v>
       </c>
       <c r="CM9">
-        <v>9.1504219768211374</v>
+        <v>9.1504219768207644</v>
       </c>
       <c r="CN9">
-        <v>12.073347841320865</v>
+        <v>12.073347841320281</v>
       </c>
       <c r="CO9">
-        <v>7.0159056276738472E-3</v>
+        <v>7.0159056276735011E-3</v>
       </c>
       <c r="CP9">
         <v>7.6310474867400391E-2</v>
       </c>
       <c r="CQ9">
-        <v>8.7837298996193292E-3</v>
+        <v>8.783729899619043E-3</v>
       </c>
       <c r="CR9">
         <v>80.841672056179775</v>
@@ -3402,8 +3596,53 @@
       <c r="DH9">
         <v>65.141173539325848</v>
       </c>
+      <c r="DI9">
+        <v>-4.4076418988764052</v>
+      </c>
+      <c r="DJ9">
+        <v>-6.4768334044943812</v>
+      </c>
+      <c r="DK9">
+        <v>-6.3888806516853931</v>
+      </c>
+      <c r="DL9">
+        <v>-7.2601139662921357</v>
+      </c>
+      <c r="DM9">
+        <v>-7.1960158988764045</v>
+      </c>
+      <c r="DN9">
+        <v>-7.7511159775280891</v>
+      </c>
+      <c r="DO9">
+        <v>-7.6381496629213466</v>
+      </c>
+      <c r="DP9">
+        <v>-7.9391272471910108</v>
+      </c>
+      <c r="DQ9">
+        <v>-7.9905059775280902</v>
+      </c>
+      <c r="DR9">
+        <v>-7.9025536966292131</v>
+      </c>
+      <c r="DS9">
+        <v>-8.0693394606741577</v>
+      </c>
+      <c r="DT9">
+        <v>-8.2604283707865171</v>
+      </c>
+      <c r="DU9">
+        <v>-8.2977698764044945</v>
+      </c>
+      <c r="DV9">
+        <v>-8.200951853932585</v>
+      </c>
+      <c r="DW9">
+        <v>-8.356580584269663</v>
+      </c>
     </row>
-    <row r="10" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>136</v>
       </c>
@@ -3429,22 +3668,22 @@
         <v>648.87940887560808</v>
       </c>
       <c r="I10">
-        <v>369.91974731671235</v>
+        <v>369.91974731671246</v>
       </c>
       <c r="J10">
-        <v>2.3752671857563512</v>
+        <v>2.375267185756353</v>
       </c>
       <c r="K10">
-        <v>1.5602263921619388</v>
+        <v>1.5602263921619401</v>
       </c>
       <c r="L10">
         <v>8.4103770364583337</v>
       </c>
       <c r="M10">
-        <v>2.6158610662319717</v>
+        <v>2.6158610662291863</v>
       </c>
       <c r="N10">
-        <v>0.31371547361025165</v>
+        <v>0.31371547360984309</v>
       </c>
       <c r="O10">
         <v>1.9872976015625028</v>
@@ -3456,13 +3695,13 @@
         <v>64.978003515624991</v>
       </c>
       <c r="R10">
-        <v>230.26050774230552</v>
+        <v>230.2605077423292</v>
       </c>
       <c r="S10">
         <v>272.21034068754904</v>
       </c>
       <c r="T10">
-        <v>0.98578055848217438</v>
+        <v>0.98578055848218127</v>
       </c>
       <c r="U10">
         <v>0.98062806391684176</v>
@@ -3477,34 +3716,34 @@
         <v>338.74254430208333</v>
       </c>
       <c r="Y10">
-        <v>651.70998102031263</v>
+        <v>651.70998102031228</v>
       </c>
       <c r="Z10">
-        <v>447.32858012411145</v>
+        <v>447.32858012386049</v>
       </c>
       <c r="AA10">
-        <v>645.53852267876118</v>
+        <v>645.53852267840148</v>
       </c>
       <c r="AB10">
-        <v>3.7033902289287247E-2</v>
+        <v>3.703390228870939E-2</v>
       </c>
       <c r="AC10">
-        <v>0.3136079035896045</v>
+        <v>0.31360790358998919</v>
       </c>
       <c r="AD10">
-        <v>9.4696391359381203E-3</v>
+        <v>9.4696391364895438E-3</v>
       </c>
       <c r="AE10">
-        <v>1.923909446813187</v>
+        <v>1.9239094468131859</v>
       </c>
       <c r="AF10">
-        <v>1.3205562385018677</v>
+        <v>1.3205562385011269</v>
       </c>
       <c r="AG10">
-        <v>1.9056907186216439</v>
+        <v>1.9056907186205818</v>
       </c>
       <c r="AH10">
-        <v>1.9234532325992735E-2</v>
+        <v>1.9234532325424714E-2</v>
       </c>
       <c r="AI10">
         <v>60.065548333333332</v>
@@ -3513,10 +3752,10 @@
         <v>25.292527848958333</v>
       </c>
       <c r="AK10">
-        <v>1.5012613018124961</v>
+        <v>1.5012613018124976</v>
       </c>
       <c r="AL10">
-        <v>350.09411909235729</v>
+        <v>350.09411909235757</v>
       </c>
       <c r="AM10">
         <v>-0.26851333333333333</v>
@@ -3531,16 +3770,16 @@
         <v>25.514614697916667</v>
       </c>
       <c r="AQ10">
-        <v>565.02872451729058</v>
+        <v>565.02872451729093</v>
       </c>
       <c r="AR10">
-        <v>663.95893689237141</v>
+        <v>663.95893689237153</v>
       </c>
       <c r="AS10">
-        <v>2.398546871983505</v>
+        <v>2.3985468719835068</v>
       </c>
       <c r="AT10">
-        <v>2.4160728405192713</v>
+        <v>2.4160728405192726</v>
       </c>
       <c r="AU10">
         <v>6.7419659097567317</v>
@@ -3549,19 +3788,19 @@
         <v>8.4103770364583337</v>
       </c>
       <c r="AW10">
-        <v>231.12232954759051</v>
+        <v>231.12232954758997</v>
       </c>
       <c r="AX10">
         <v>338.74254430208333</v>
       </c>
       <c r="AY10">
-        <v>0.68229495655402694</v>
+        <v>0.68229495655402539</v>
       </c>
       <c r="AZ10">
-        <v>2258.661754152482</v>
+        <v>2258.6617541524811</v>
       </c>
       <c r="BA10">
-        <v>2.1206563264687887E-2</v>
+        <v>2.1206563264687058E-2</v>
       </c>
       <c r="BB10">
         <v>-6.6672273072916672</v>
@@ -3576,25 +3815,25 @@
         <v>3.7844473020833331</v>
       </c>
       <c r="BF10">
-        <v>350.09411909235729</v>
+        <v>350.09411909235757</v>
       </c>
       <c r="BG10">
-        <v>559.02506229145979</v>
+        <v>559.0250622914599</v>
       </c>
       <c r="BH10">
-        <v>1.5012613018124961</v>
+        <v>1.5012613018124976</v>
       </c>
       <c r="BI10">
-        <v>2.3763995877204751</v>
+        <v>2.3763995877204764</v>
       </c>
       <c r="BJ10">
-        <v>2.9174743960270297</v>
+        <v>2.9174743960249834</v>
       </c>
       <c r="BK10">
-        <v>6.5162858647770303</v>
+        <v>6.5162858647749839</v>
       </c>
       <c r="BL10">
-        <v>0.46819724624029097</v>
+        <v>0.46819722638027894</v>
       </c>
       <c r="BM10">
         <v>8.4103770364583337</v>
@@ -3615,16 +3854,16 @@
         <v>338.74254430208333</v>
       </c>
       <c r="BS10">
-        <v>488.10777969092004</v>
+        <v>488.10777969091959</v>
       </c>
       <c r="BT10">
         <v>450.24906767580984</v>
       </c>
       <c r="BU10">
-        <v>7.7562197511138048E-2</v>
+        <v>7.7562197511137201E-2</v>
       </c>
       <c r="BV10">
-        <v>1.4409402890226743</v>
+        <v>1.440940289022673</v>
       </c>
       <c r="BW10">
         <v>1.3291777937237415</v>
@@ -3645,49 +3884,49 @@
         <v>230</v>
       </c>
       <c r="CC10">
-        <v>13.556130016054881</v>
+        <v>13.556130016055624</v>
       </c>
       <c r="CD10">
-        <v>18.60051557228736</v>
+        <v>18.60051557228595</v>
       </c>
       <c r="CE10">
-        <v>18.620262027265216</v>
+        <v>18.620262027265266</v>
       </c>
       <c r="CF10">
-        <v>29.605100887027959</v>
+        <v>29.605100887027447</v>
       </c>
       <c r="CG10">
-        <v>4.5861090929441434E-2</v>
+        <v>4.5861090929466199E-2</v>
       </c>
       <c r="CH10">
-        <v>8.7397055330099796E-2</v>
+        <v>8.7397055330098283E-2</v>
       </c>
       <c r="CI10">
-        <v>9.5284535931082198E-3</v>
+        <v>9.528453593102908E-3</v>
       </c>
       <c r="CJ10">
-        <v>8.791494018793701E-2</v>
+        <v>8.7914940187934928E-2</v>
       </c>
       <c r="CK10">
-        <v>4.6132847963663542E-2</v>
+        <v>4.6132847963688155E-2</v>
       </c>
       <c r="CL10">
-        <v>8.1119008323452793</v>
+        <v>8.1119008323440145</v>
       </c>
       <c r="CM10">
-        <v>17.71958015096525</v>
+        <v>17.719580150966017</v>
       </c>
       <c r="CN10">
-        <v>19.488110627772148</v>
+        <v>19.488110627772318</v>
       </c>
       <c r="CO10">
-        <v>8.6281669187269136E-3</v>
+        <v>8.6281669187269934E-3</v>
       </c>
       <c r="CP10">
-        <v>6.7310691042382201E-2</v>
+        <v>6.7310691042362231E-2</v>
       </c>
       <c r="CQ10">
-        <v>1.2618159251379824E-2</v>
+        <v>1.2618159251379723E-2</v>
       </c>
       <c r="CR10">
         <v>80.042486645833336</v>
@@ -3739,6 +3978,51 @@
       </c>
       <c r="DH10">
         <v>66.037128895833334</v>
+      </c>
+      <c r="DI10">
+        <v>-3.8673248020833335</v>
+      </c>
+      <c r="DJ10">
+        <v>-5.9048960364583332</v>
+      </c>
+      <c r="DK10">
+        <v>-6.3556113854166663</v>
+      </c>
+      <c r="DL10">
+        <v>-7.0432814270833335</v>
+      </c>
+      <c r="DM10">
+        <v>-6.8245359583333327</v>
+      </c>
+      <c r="DN10">
+        <v>-7.2806008177083328</v>
+      </c>
+      <c r="DO10">
+        <v>-7.0302227239583344</v>
+      </c>
+      <c r="DP10">
+        <v>-7.1968522291666668</v>
+      </c>
+      <c r="DQ10">
+        <v>-7.0871424166666666</v>
+      </c>
+      <c r="DR10">
+        <v>-6.8811310208333341</v>
+      </c>
+      <c r="DS10">
+        <v>-6.9659269479166666</v>
+      </c>
+      <c r="DT10">
+        <v>-6.9794051197916671</v>
+      </c>
+      <c r="DU10">
+        <v>-6.8937478645833332</v>
+      </c>
+      <c r="DV10">
+        <v>-6.6530409947916667</v>
+      </c>
+      <c r="DW10">
+        <v>-6.6672273072916672</v>
       </c>
     </row>
   </sheetData>
